--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -35,9 +35,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="177" formatCode="yyyy/MM/dd HH:mm:ss"/>
-    <numFmt numFmtId="178" formatCode="yyyy/MM/dd"/>
+  <numFmts count="3">
+    <numFmt numFmtId="177" formatCode="yyyy/MM/dd HH:mm:ss z"/>
+    <numFmt numFmtId="178" formatCode="yyyy/MM/dd HH:mm:ss"/>
+    <numFmt numFmtId="179" formatCode="yyyy/MM/dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -75,8 +76,11 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -494,7 +498,7 @@
       <c r="B2" s="2">
         <v>44105.270833333336</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -40,8 +40,15 @@
     <numFmt numFmtId="178" formatCode="yyyy/MM/dd HH:mm:ss"/>
     <numFmt numFmtId="179" formatCode="yyyy/MM/dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -76,8 +83,9 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -475,30 +483,30 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="16.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="20.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="26.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="17.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="22.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="27.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14" customHeight="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14" customHeight="1">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>44105</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>44105.270833333336</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
     </row>

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$2</definedName>

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -488,7 +488,7 @@
     <col min="3" max="3" width="27.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14" customHeight="1">
+    <row r="1" spans="1:3" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14" customHeight="1">
+    <row r="2" spans="1:3" ht="16" customHeight="1">
       <c r="A2" s="2">
         <v>44105</v>
       </c>

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -488,7 +488,7 @@
     <col min="3" max="3" width="27.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" customHeight="1">
+    <row r="1" spans="1:3" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" customHeight="1">
+    <row r="2" spans="1:3" ht="14" customHeight="1">
       <c r="A2" s="2">
         <v>44105</v>
       </c>

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
   </sheets>
 </workbook>
 </file>
@@ -43,15 +43,15 @@
     </border>
   </borders>
   <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -99,4 +99,14 @@
   </sheetData>
   <autoFilter ref="A1:C2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/VerifyTests/Verify.OpenXml/v1/columnMetadata">
+  <sheet name="Sheet1">
+    <column index="1" property="DateProperty"/>
+    <column index="2" property="DateTimeProperty"/>
+    <column index="3" property="DateTimeOffsetProperty"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -102,7 +102,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/VerifyTests/Verify.OpenXml/v1/columnMetadata">
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="DateProperty"/>
     <column index="2" property="DateTimeProperty"/>

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -99,4 +99,14 @@
   </sheetData>
   <autoFilter ref="A1:C2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="DateProperty"/>
+    <column index="2" property="DateTimeProperty"/>
+    <column index="3" property="DateTimeOffsetProperty"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -9,10 +9,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/MM/dd"/>
     <numFmt numFmtId="165" formatCode="yyyy/MM/dd HH:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy/MM/dd HH:mm:ss z"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -51,7 +50,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -61,7 +61,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
   </cols>
   <sheetData>

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -60,9 +60,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
+++ b/src/StaticSettingsTests/DateFormats.Test.verified.xlsx
@@ -60,9 +60,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
